--- a/config/excel/CfgQualities.xlsx
+++ b/config/excel/CfgQualities.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgQualities" sheetId="1" r:id="Rff28bf263f254aaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgQualities" sheetId="1" r:id="Rdfb2b81f79cb4083"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="General"/>
+    <x:numFmt numFmtId="201" formatCode="@"/>
+  </x:numFmts>
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +37,14 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +59,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -63,7 +88,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -90,6 +115,26 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -301,267 +346,295 @@
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>Name</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>ColorR</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>ColorG</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>ColorB</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>Weight</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>AffixCount</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>ScaleMin</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>ScaleMax</x:v>
       </x:c>
+      <x:c r="J1" s="12" t="str">
+        <x:v>AdvancedAffixCount</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="13" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="G2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
+      <x:c r="H2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="I2" s="6" t="str">
+      <x:c r="I2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="15" t="str">
         <x:v># 品质枚举值</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="15" t="str">
         <x:v>品质名称</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="15" t="str">
         <x:v>颜色红色分量</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="15" t="str">
         <x:v>颜色绿色分量</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="15" t="str">
         <x:v>颜色蓝色分量</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="15" t="str">
         <x:v>掉落品质权重</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
+      <x:c r="G3" s="15" t="str">
         <x:v>随机词条数量</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="15" t="str">
         <x:v>词条倍率最小值</x:v>
       </x:c>
-      <x:c r="I3" s="8" t="str">
+      <x:c r="I3" s="15" t="str">
         <x:v>词条倍率最大值</x:v>
       </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>独立高级词条数量；旧装备不补抽</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="3" t="n">
+      <x:c r="A4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="18" t="str">
         <x:v>普通</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="n">
+      <x:c r="C4" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="17" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="n">
+      <x:c r="G4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="n">
+      <x:c r="H4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="n">
+      <x:c r="I4" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J4" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="A5" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="str">
         <x:v>精良</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="n">
+      <x:c r="C5" s="17" t="n">
         <x:v>0.28</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
+      <x:c r="D5" s="17" t="n">
         <x:v>0.82</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="n">
+      <x:c r="E5" s="17" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="n">
+      <x:c r="F5" s="17" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="n">
+      <x:c r="G5" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="17" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="n">
+      <x:c r="I5" s="17" t="n">
         <x:v>1.1</x:v>
       </x:c>
+      <x:c r="J5" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="3" t="n">
+      <x:c r="A6" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="9" t="str">
+      <x:c r="B6" s="18" t="str">
         <x:v>优秀</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="n">
+      <x:c r="C6" s="17" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="n">
+      <x:c r="D6" s="17" t="n">
         <x:v>0.56</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="3" t="n">
+      <x:c r="E6" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="17" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="n">
+      <x:c r="G6" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="n">
+      <x:c r="H6" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="n">
         <x:v>1.5</x:v>
       </x:c>
+      <x:c r="J6" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="3" t="n">
+      <x:c r="A7" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="str">
+      <x:c r="B7" s="18" t="str">
         <x:v>史诗</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="n">
+      <x:c r="C7" s="17" t="n">
         <x:v>0.68</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="n">
+      <x:c r="D7" s="17" t="n">
         <x:v>0.36</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="n">
+      <x:c r="E7" s="17" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="n">
+      <x:c r="F7" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="n">
+      <x:c r="G7" s="17" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="n">
+      <x:c r="H7" s="17" t="n">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="n">
+      <x:c r="I7" s="17" t="n">
         <x:v>1.9</x:v>
       </x:c>
+      <x:c r="J7" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="3" t="n">
+      <x:c r="A8" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="str">
+      <x:c r="B8" s="18" t="str">
         <x:v>传说</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="3" t="n">
+      <x:c r="C8" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="n">
         <x:v>0.62</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="n">
+      <x:c r="E8" s="17" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="n">
+      <x:c r="F8" s="17" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="n">
+      <x:c r="G8" s="17" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="n">
+      <x:c r="H8" s="17" t="n">
         <x:v>1.7</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="n">
+      <x:c r="I8" s="17" t="n">
         <x:v>2.4</x:v>
       </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="3" t="n">
+      <x:c r="A9" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="str">
+      <x:c r="B9" s="18" t="str">
         <x:v>神器</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="n">
+      <x:c r="C9" s="17" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="n">
+      <x:c r="D9" s="17" t="n">
         <x:v>0.22</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="n">
+      <x:c r="E9" s="17" t="n">
         <x:v>0.24</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="3" t="n">
+      <x:c r="F9" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="n">
+      <x:c r="H9" s="17" t="n">
         <x:v>2.2</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="n">
+      <x:c r="I9" s="17" t="n">
         <x:v>3</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
